--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488130_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488130_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5734</v>
+        <v>3.9191</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7841</v>
+        <v>3.9574</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2106</v>
+        <v>-0.0383</v>
       </c>
       <c r="G2" t="n">
         <v>0.7735</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0588</v>
+        <v>0.4045</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6179</v>
+        <v>0.7912</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5591</v>
+        <v>-0.3868</v>
       </c>
       <c r="V2" t="n">
         <v>1.2589</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1316</v>
+        <v>3.7569</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3294</v>
+        <v>3.0039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8022</v>
+        <v>0.753</v>
       </c>
       <c r="G3" t="n">
         <v>2.41</v>
@@ -688,13 +688,13 @@
         <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6835</v>
+        <v>0.3087</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7126</v>
+        <v>0.3871</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0291</v>
+        <v>-0.0784</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6995</v>
+        <v>3.0529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9405</v>
+        <v>1.4417</v>
       </c>
       <c r="F4" t="n">
-        <v>1.759</v>
+        <v>1.6113</v>
       </c>
       <c r="G4" t="n">
         <v>1.6738</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0861</v>
+        <v>0.2674</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5931</v>
+        <v>-0.092</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5071</v>
+        <v>0.3594</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2315</v>
+        <v>2.3601</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2848</v>
+        <v>1.3395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9467</v>
+        <v>1.0206</v>
       </c>
       <c r="G5" t="n">
         <v>4.5574</v>
@@ -844,13 +844,13 @@
         <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0828</v>
+        <v>0.2114</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3071</v>
+        <v>-0.2524</v>
       </c>
       <c r="U5" t="n">
-        <v>0.39</v>
+        <v>0.4638</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3853</v>
+        <v>0.3541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.4838</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2282</v>
+        <v>-0.1297</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2348</v>
@@ -922,13 +922,13 @@
         <v>2.2234</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3231</v>
+        <v>0.2919</v>
       </c>
       <c r="T6" t="n">
-        <v>0.582</v>
+        <v>0.4524</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2589</v>
+        <v>-0.1604</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2978</v>
+        <v>0.3225</v>
       </c>
       <c r="E7" t="n">
         <v>0.195</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1028</v>
+        <v>0.1275</v>
       </c>
       <c r="G7" t="n">
         <v>0.0414</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0711</v>
+        <v>0.0958</v>
       </c>
       <c r="T7" t="n">
         <v>0.1306</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0594</v>
+        <v>-0.0348</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3866</v>
+        <v>0.0297</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0453</v>
+        <v>0.3464</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3413</v>
+        <v>-0.3167</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3483</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4089</v>
+        <v>0.0075</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0883</v>
+        <v>0.3034</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3206</v>
+        <v>-0.296</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7088</v>
+        <v>-1.4867</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3794</v>
+        <v>-1.7141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6706</v>
+        <v>0.2274</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2801</v>
@@ -1156,13 +1156,13 @@
         <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4034</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2686</v>
+        <v>0.3967</v>
       </c>
       <c r="U9" t="n">
-        <v>0.672</v>
+        <v>0.2288</v>
       </c>
       <c r="V9" t="n">
         <v>0.315</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0273</v>
+        <v>-1.8796</v>
       </c>
       <c r="E10" t="n">
         <v>-1.7888</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2385</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4095</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2298</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2524</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0226</v>
+        <v>0.1704</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5733</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5275</v>
+        <v>-4.0855</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1854</v>
+        <v>-0.2495</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7129</v>
+        <v>-3.836</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3611</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7225</v>
+        <v>0.1645</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8767</v>
+        <v>0.4418</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1542</v>
+        <v>-0.2773</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5183</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0155</v>
+        <v>-5.5959</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9097</v>
+        <v>-5.3423</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1058</v>
+        <v>-0.2536</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7353</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2385</v>
+        <v>0.6581</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5633</v>
+        <v>0.0041</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8018</v>
+        <v>0.6541</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5188</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4049</v>
+        <v>-6.1312</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4773</v>
+        <v>-4.573</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9276</v>
+        <v>-1.5583</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7421</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4039</v>
+        <v>-0.1303</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2497</v>
+        <v>-0.3454</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1542</v>
+        <v>0.2151</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5177</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.751500000000001</v>
+        <v>-5.383599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.267900000000002</v>
+        <v>-2.900000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-2.4836</v>
@@ -1546,13 +1546,13 @@
         <v>16.6759</v>
       </c>
       <c r="S14" t="n">
-        <v>1.455</v>
+        <v>2.8229</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5972999999999999</v>
+        <v>1.9651</v>
       </c>
       <c r="U14" t="n">
-        <v>0.858</v>
+        <v>0.8579000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-8.1836</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5024</v>
+        <v>6.7144</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7169</v>
+        <v>4.6201</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7855</v>
+        <v>2.0943</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4222</v>
+        <v>6.0012</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0966</v>
+        <v>2.1965</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3256</v>
+        <v>3.8047</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6476</v>
+        <v>5.136</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4911</v>
+        <v>2.4605</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1565</v>
+        <v>2.6755</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2254</v>
+        <v>0.8652</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3945</v>
+        <v>-0.264</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1692</v>
+        <v>1.1292</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0382</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9646</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0269</v>
+        <v>0.1775</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2574</v>
+        <v>0.2459</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7695</v>
+        <v>-0.0684</v>
       </c>
       <c r="V15" t="n">
-        <v>4.0915</v>
+        <v>2.2033</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7766</v>
+        <v>2.2027</v>
       </c>
       <c r="X15" t="n">
-        <v>0.315</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7002</v>
+        <v>6.3771</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1304</v>
+        <v>4.7169</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5698</v>
+        <v>1.6602</v>
       </c>
       <c r="G16" t="n">
-        <v>6.0012</v>
+        <v>3.4222</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1965</v>
+        <v>3.0966</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8047</v>
+        <v>0.3256</v>
       </c>
       <c r="J16" t="n">
-        <v>5.136</v>
+        <v>3.6476</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4605</v>
+        <v>3.4911</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6755</v>
+        <v>0.1565</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8652</v>
+        <v>-0.2254</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.264</v>
+        <v>-0.3945</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1292</v>
+        <v>0.1692</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6676</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9646</v>
       </c>
       <c r="R16" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8367</v>
+        <v>0.9015</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2437</v>
+        <v>0.2574</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5929</v>
+        <v>0.6441</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2033</v>
+        <v>4.0915</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2027</v>
+        <v>3.7766</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0005</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0292</v>
+        <v>4.6837</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3155</v>
+        <v>3.4134</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7137</v>
+        <v>1.2703</v>
       </c>
       <c r="G17" t="n">
         <v>2.3545</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6959</v>
+        <v>-0.0414</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.286</v>
+        <v>-0.1881</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4099</v>
+        <v>0.1467</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2326</v>
+        <v>0.4102</v>
       </c>
       <c r="E19" t="n">
         <v>-1.2265</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4591</v>
+        <v>1.6367</v>
       </c>
       <c r="G19" t="n">
         <v>3.1119</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4728</v>
+        <v>0.6504</v>
       </c>
       <c r="T19" t="n">
         <v>0.1144</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3584</v>
+        <v>0.5359</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9433</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0673</v>
+        <v>0.2701</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2639</v>
+        <v>1.6852</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3312</v>
+        <v>-1.4151</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2887</v>
+        <v>0.9454</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2167</v>
+        <v>-0.7857</v>
       </c>
       <c r="I20" t="n">
-        <v>0.928</v>
+        <v>1.7311</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4716</v>
+        <v>1.9721</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.384</v>
+        <v>0.0644</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9124</v>
+        <v>1.9077</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8171</v>
+        <v>-1.0267</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8327</v>
+        <v>-0.8501</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0156</v>
+        <v>-0.1766</v>
       </c>
       <c r="P20" t="n">
         <v>0.9264</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7996</v>
+        <v>-0.3429</v>
       </c>
       <c r="T20" t="n">
-        <v>0.005</v>
+        <v>-0.2869</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7946</v>
+        <v>-0.056</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3155</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5385</v>
+        <v>0.1149</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3914</v>
+        <v>-2.3618</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9299</v>
+        <v>2.4767</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9454</v>
+        <v>-2.2887</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7857</v>
+        <v>-3.2167</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7311</v>
+        <v>0.928</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9721</v>
+        <v>-1.4716</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0644</v>
+        <v>-2.384</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9077</v>
+        <v>0.9124</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0267</v>
+        <v>-0.8171</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8501</v>
+        <v>-0.8327</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1766</v>
+        <v>0.0156</v>
       </c>
       <c r="P21" t="n">
         <v>0.9264</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1515</v>
+        <v>0.8472</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5807</v>
+        <v>-0.0929</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5708</v>
+        <v>0.9401</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2589</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4673</v>
+        <v>-0.9686</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9225</v>
+        <v>-1.1183</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5449000000000001</v>
+        <v>0.1497</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2254</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4621</v>
+        <v>0.0367</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.235</v>
+        <v>-0.4309</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2271</v>
+        <v>0.4675</v>
       </c>
       <c r="V22" t="n">
         <v>1.8877</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3013</v>
+        <v>-2.2596</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0907</v>
+        <v>-2.4824</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2106</v>
+        <v>0.2229</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5242</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2594</v>
+        <v>-0.2176</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0386</v>
+        <v>-0.3531</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.298</v>
+        <v>0.1355</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4171</v>
+        <v>-6.2705</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5112</v>
+        <v>-5.7071</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9059</v>
+        <v>-0.5635</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0859</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3487</v>
+        <v>-0.2021</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0721</v>
+        <v>-0.1237</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4208</v>
+        <v>-0.0784</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.7516</v>
+        <v>10.0158</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4835</v>
+        <v>2.4836</v>
       </c>
       <c r="F25" t="n">
-        <v>4.268</v>
+        <v>7.532199999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>4.655100000000002</v>
+        <v>4.6551</v>
       </c>
       <c r="H25" t="n">
         <v>-2.7564</v>
@@ -2404,13 +2404,13 @@
         <v>12.0436</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.455</v>
+        <v>1.8093</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8578999999999999</v>
+        <v>-0.8579</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.597</v>
+        <v>2.667</v>
       </c>
       <c r="V25" t="n">
         <v>8.1836</v>
